--- a/config/divergent-universe-generated/templates/DivergentUniverseBindings.xlsx
+++ b/config/divergent-universe-generated/templates/DivergentUniverseBindings.xlsx
@@ -54,7 +54,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>3f3690d8ff32ac1e</t>
+    <t>7cd119db777582fe</t>
   </si>
   <si>
     <t>#name</t>
@@ -126,13 +126,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>enum&lt;DUOwnership&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;DUCoverageState&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;DUEvidenceQuality&gt;</t>
+    <t>enum&lt;DuOwnership&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;DuCoverageState&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;DuEvidenceQuality&gt;</t>
   </si>
   <si>
     <t>optional&lt;list&lt;ref&lt;DivergentUniverseSources.id&gt;&gt;&gt;</t>
@@ -180,7 +180,7 @@
     <t>DivergentUniverseCurioPoolMembership</t>
   </si>
   <si>
-    <t>f9e4811f4ff2d7f5</t>
+    <t>cc7e0f1d4f270055</t>
   </si>
   <si>
     <t>curio_state_id</t>
@@ -198,7 +198,7 @@
     <t>DivergentUniverseOccurrences</t>
   </si>
   <si>
-    <t>056d1b6b8b9ca5c4</t>
+    <t>955528d2e29fc624</t>
   </si>
   <si>
     <t>variant_ids</t>
@@ -219,7 +219,7 @@
     <t>DivergentUniverseOccurrenceVariants</t>
   </si>
   <si>
-    <t>69e9ff91a85b032a</t>
+    <t>86b5202416146b0a</t>
   </si>
   <si>
     <t>occurrence_id</t>
@@ -243,7 +243,7 @@
     <t>DivergentUniverseOccurrenceChoices</t>
   </si>
   <si>
-    <t>893dd573b494184e</t>
+    <t>be1734f5280907ee</t>
   </si>
   <si>
     <t>variant_id</t>
@@ -264,7 +264,7 @@
     <t>DivergentUniverseModeServiceNpcs</t>
   </si>
   <si>
-    <t>0f32e0ed89553058</t>
+    <t>3f08015f240f6a38</t>
   </si>
   <si>
     <t>service_kind</t>
@@ -273,7 +273,7 @@
     <t>DivergentUniverseAdventureOutcomes</t>
   </si>
   <si>
-    <t>0fb72584caf02c02</t>
+    <t>e969758c7fdc3a22</t>
   </si>
   <si>
     <t>adventure_type</t>
@@ -288,7 +288,7 @@
     <t>DivergentUniverseEncounterSourceObligations</t>
   </si>
   <si>
-    <t>116b6dfe5e9af983</t>
+    <t>9caff36f651887a3</t>
   </si>
   <si>
     <t>encounter_group_ids</t>
@@ -309,7 +309,7 @@
     <t>DivergentUniverseEncounterGroups</t>
   </si>
   <si>
-    <t>495e6ac76e7b854a</t>
+    <t>4bba3e9765d7912a</t>
   </si>
   <si>
     <t>module_id</t>
@@ -327,7 +327,7 @@
     <t>DivergentUniverseEncounterWaves</t>
   </si>
   <si>
-    <t>e55f947df9f46b8c</t>
+    <t>0b7139348892b2ac</t>
   </si>
   <si>
     <t>enemy_slot_ids</t>
@@ -348,7 +348,7 @@
     <t>DivergentUniverseEnemySlots</t>
   </si>
   <si>
-    <t>f8ee8f81a97c7589</t>
+    <t>50695979c4a83ae9</t>
   </si>
   <si>
     <t>wave_id</t>
@@ -372,7 +372,7 @@
     <t>DivergentUniverseBossPools</t>
   </si>
   <si>
-    <t>c5f7baeb21abfac4</t>
+    <t>83266e667b21f524</t>
   </si>
   <si>
     <t>weekly_modifier_id</t>
@@ -1180,14 +1180,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1573,14 +1573,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1978,14 +1978,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2399,14 +2399,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2790,14 +2790,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3171,14 +3171,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3580,14 +3580,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3983,14 +3983,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4358,14 +4358,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4735,14 +4735,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5128,14 +5128,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5518,14 +5518,14 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DUOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DUCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DUEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
